--- a/Dataset/Food Prices/PIHPS/Wholesale/Tabel Harga Berdasarkan Daerah 2026.xlsx
+++ b/Dataset/Food Prices/PIHPS/Wholesale/Tabel Harga Berdasarkan Daerah 2026.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN32"/>
+  <dimension ref="A1:AO32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.43" customWidth="1" min="1" max="1"/>
@@ -467,6 +467,7 @@
     <col width="8.859999999999999" customWidth="1" min="38" max="38"/>
     <col width="8.859999999999999" customWidth="1" min="39" max="39"/>
     <col width="8.859999999999999" customWidth="1" min="40" max="40"/>
+    <col width="8.859999999999999" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -670,6 +671,11 @@
           <t>17/ 09/ 2026</t>
         </is>
       </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>24/ 09/ 2026</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -872,6 +878,11 @@
           <t>15,550</t>
         </is>
       </c>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>15,550</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1074,6 +1085,11 @@
           <t>14,500</t>
         </is>
       </c>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>14,450</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1276,6 +1292,11 @@
           <t>14,050</t>
         </is>
       </c>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>14,050</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1478,6 +1499,11 @@
           <t>15,600</t>
         </is>
       </c>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>15,600</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1680,6 +1706,11 @@
           <t>15,450</t>
         </is>
       </c>
+      <c r="AO6" s="2" t="inlineStr">
+        <is>
+          <t>15,450</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1882,6 +1913,11 @@
           <t>16,850</t>
         </is>
       </c>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>16,900</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2084,6 +2120,11 @@
           <t>16,400</t>
         </is>
       </c>
+      <c r="AO8" s="2" t="inlineStr">
+        <is>
+          <t>16,400</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2286,6 +2327,11 @@
           <t>35,600</t>
         </is>
       </c>
+      <c r="AO9" s="2" t="inlineStr">
+        <is>
+          <t>35,650</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2488,6 +2534,11 @@
           <t>35,600</t>
         </is>
       </c>
+      <c r="AO10" s="2" t="inlineStr">
+        <is>
+          <t>35,650</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2690,6 +2741,11 @@
           <t>139,400</t>
         </is>
       </c>
+      <c r="AO11" s="2" t="inlineStr">
+        <is>
+          <t>139,850</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2892,6 +2948,11 @@
           <t>143,400</t>
         </is>
       </c>
+      <c r="AO12" s="2" t="inlineStr">
+        <is>
+          <t>143,900</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3094,6 +3155,11 @@
           <t>134,650</t>
         </is>
       </c>
+      <c r="AO13" s="2" t="inlineStr">
+        <is>
+          <t>135,100</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3296,6 +3362,11 @@
           <t>26,200</t>
         </is>
       </c>
+      <c r="AO14" s="2" t="inlineStr">
+        <is>
+          <t>26,300</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3498,6 +3569,11 @@
           <t>26,200</t>
         </is>
       </c>
+      <c r="AO15" s="2" t="inlineStr">
+        <is>
+          <t>26,300</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3700,6 +3776,11 @@
           <t>29,450</t>
         </is>
       </c>
+      <c r="AO16" s="2" t="inlineStr">
+        <is>
+          <t>29,600</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3902,6 +3983,11 @@
           <t>29,450</t>
         </is>
       </c>
+      <c r="AO17" s="2" t="inlineStr">
+        <is>
+          <t>29,600</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4104,6 +4190,11 @@
           <t>30,650</t>
         </is>
       </c>
+      <c r="AO18" s="2" t="inlineStr">
+        <is>
+          <t>30,500</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4306,6 +4397,11 @@
           <t>30,650</t>
         </is>
       </c>
+      <c r="AO19" s="2" t="inlineStr">
+        <is>
+          <t>30,500</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4505,7 +4601,12 @@
       </c>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>53,400</t>
+          <t>53,450</t>
+        </is>
+      </c>
+      <c r="AO20" s="2" t="inlineStr">
+        <is>
+          <t>54,100</t>
         </is>
       </c>
     </row>
@@ -4710,6 +4811,11 @@
           <t>44,200</t>
         </is>
       </c>
+      <c r="AO21" s="2" t="inlineStr">
+        <is>
+          <t>44,650</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4909,7 +5015,12 @@
       </c>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>56,200</t>
+          <t>56,250</t>
+        </is>
+      </c>
+      <c r="AO22" s="2" t="inlineStr">
+        <is>
+          <t>56,550</t>
         </is>
       </c>
     </row>
@@ -5114,6 +5225,11 @@
           <t>70,150</t>
         </is>
       </c>
+      <c r="AO23" s="2" t="inlineStr">
+        <is>
+          <t>70,300</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5316,6 +5432,11 @@
           <t>59,000</t>
         </is>
       </c>
+      <c r="AO24" s="2" t="inlineStr">
+        <is>
+          <t>59,400</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5518,6 +5639,11 @@
           <t>79,950</t>
         </is>
       </c>
+      <c r="AO25" s="2" t="inlineStr">
+        <is>
+          <t>79,850</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5720,6 +5846,11 @@
           <t>21,100</t>
         </is>
       </c>
+      <c r="AO26" s="2" t="inlineStr">
+        <is>
+          <t>21,100</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5922,6 +6053,11 @@
           <t>18,700</t>
         </is>
       </c>
+      <c r="AO27" s="2" t="inlineStr">
+        <is>
+          <t>18,750</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -6124,6 +6260,11 @@
           <t>22,200</t>
         </is>
       </c>
+      <c r="AO28" s="2" t="inlineStr">
+        <is>
+          <t>22,200</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6326,6 +6467,11 @@
           <t>21,700</t>
         </is>
       </c>
+      <c r="AO29" s="2" t="inlineStr">
+        <is>
+          <t>21,700</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6528,6 +6674,11 @@
           <t>17,950</t>
         </is>
       </c>
+      <c r="AO30" s="2" t="inlineStr">
+        <is>
+          <t>18,000</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6730,6 +6881,11 @@
           <t>18,650</t>
         </is>
       </c>
+      <c r="AO31" s="2" t="inlineStr">
+        <is>
+          <t>18,700</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6930,6 +7086,11 @@
       <c r="AN32" s="2" t="inlineStr">
         <is>
           <t>17,500</t>
+        </is>
+      </c>
+      <c r="AO32" s="2" t="inlineStr">
+        <is>
+          <t>17,550</t>
         </is>
       </c>
     </row>

--- a/Dataset/Food Prices/PIHPS/Wholesale/Tabel Harga Berdasarkan Daerah 2026.xlsx
+++ b/Dataset/Food Prices/PIHPS/Wholesale/Tabel Harga Berdasarkan Daerah 2026.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO32"/>
+  <dimension ref="A1:AP32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.43" customWidth="1" min="1" max="1"/>
@@ -468,6 +468,7 @@
     <col width="8.859999999999999" customWidth="1" min="39" max="39"/>
     <col width="8.859999999999999" customWidth="1" min="40" max="40"/>
     <col width="8.859999999999999" customWidth="1" min="41" max="41"/>
+    <col width="8.859999999999999" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -676,6 +677,11 @@
           <t>24/ 09/ 2026</t>
         </is>
       </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>01/ 10/ 2026</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -883,6 +889,11 @@
           <t>15,550</t>
         </is>
       </c>
+      <c r="AP2" s="2" t="inlineStr">
+        <is>
+          <t>15,500</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1090,6 +1101,11 @@
           <t>14,450</t>
         </is>
       </c>
+      <c r="AP3" s="2" t="inlineStr">
+        <is>
+          <t>14,450</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1297,6 +1313,11 @@
           <t>14,050</t>
         </is>
       </c>
+      <c r="AP4" s="2" t="inlineStr">
+        <is>
+          <t>14,000</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1504,6 +1525,11 @@
           <t>15,600</t>
         </is>
       </c>
+      <c r="AP5" s="2" t="inlineStr">
+        <is>
+          <t>15,600</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1711,6 +1737,11 @@
           <t>15,450</t>
         </is>
       </c>
+      <c r="AP6" s="2" t="inlineStr">
+        <is>
+          <t>15,450</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1918,6 +1949,11 @@
           <t>16,900</t>
         </is>
       </c>
+      <c r="AP7" s="2" t="inlineStr">
+        <is>
+          <t>16,850</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2125,6 +2161,11 @@
           <t>16,400</t>
         </is>
       </c>
+      <c r="AP8" s="2" t="inlineStr">
+        <is>
+          <t>16,400</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2332,6 +2373,11 @@
           <t>35,650</t>
         </is>
       </c>
+      <c r="AP9" s="2" t="inlineStr">
+        <is>
+          <t>35,550</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2539,6 +2585,11 @@
           <t>35,650</t>
         </is>
       </c>
+      <c r="AP10" s="2" t="inlineStr">
+        <is>
+          <t>35,550</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2746,6 +2797,11 @@
           <t>139,850</t>
         </is>
       </c>
+      <c r="AP11" s="2" t="inlineStr">
+        <is>
+          <t>139,800</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2953,6 +3009,11 @@
           <t>143,900</t>
         </is>
       </c>
+      <c r="AP12" s="2" t="inlineStr">
+        <is>
+          <t>143,850</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3160,6 +3221,11 @@
           <t>135,100</t>
         </is>
       </c>
+      <c r="AP13" s="2" t="inlineStr">
+        <is>
+          <t>135,000</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3367,6 +3433,11 @@
           <t>26,300</t>
         </is>
       </c>
+      <c r="AP14" s="2" t="inlineStr">
+        <is>
+          <t>26,200</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3574,6 +3645,11 @@
           <t>26,300</t>
         </is>
       </c>
+      <c r="AP15" s="2" t="inlineStr">
+        <is>
+          <t>26,200</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3781,6 +3857,11 @@
           <t>29,600</t>
         </is>
       </c>
+      <c r="AP16" s="2" t="inlineStr">
+        <is>
+          <t>29,150</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3988,6 +4069,11 @@
           <t>29,600</t>
         </is>
       </c>
+      <c r="AP17" s="2" t="inlineStr">
+        <is>
+          <t>29,150</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4195,6 +4281,11 @@
           <t>30,500</t>
         </is>
       </c>
+      <c r="AP18" s="2" t="inlineStr">
+        <is>
+          <t>30,550</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4402,6 +4493,11 @@
           <t>30,500</t>
         </is>
       </c>
+      <c r="AP19" s="2" t="inlineStr">
+        <is>
+          <t>30,550</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4609,6 +4705,11 @@
           <t>54,100</t>
         </is>
       </c>
+      <c r="AP20" s="2" t="inlineStr">
+        <is>
+          <t>59,500</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4816,6 +4917,11 @@
           <t>44,650</t>
         </is>
       </c>
+      <c r="AP21" s="2" t="inlineStr">
+        <is>
+          <t>49,850</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -5023,6 +5129,11 @@
           <t>56,550</t>
         </is>
       </c>
+      <c r="AP22" s="2" t="inlineStr">
+        <is>
+          <t>62,550</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5230,6 +5341,11 @@
           <t>70,300</t>
         </is>
       </c>
+      <c r="AP23" s="2" t="inlineStr">
+        <is>
+          <t>74,900</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5437,6 +5553,11 @@
           <t>59,400</t>
         </is>
       </c>
+      <c r="AP24" s="2" t="inlineStr">
+        <is>
+          <t>61,250</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5644,6 +5765,11 @@
           <t>79,850</t>
         </is>
       </c>
+      <c r="AP25" s="2" t="inlineStr">
+        <is>
+          <t>84,850</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5851,6 +5977,11 @@
           <t>21,100</t>
         </is>
       </c>
+      <c r="AP26" s="2" t="inlineStr">
+        <is>
+          <t>21,100</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -6058,6 +6189,11 @@
           <t>18,750</t>
         </is>
       </c>
+      <c r="AP27" s="2" t="inlineStr">
+        <is>
+          <t>18,700</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -6265,6 +6401,11 @@
           <t>22,200</t>
         </is>
       </c>
+      <c r="AP28" s="2" t="inlineStr">
+        <is>
+          <t>22,150</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6472,6 +6613,11 @@
           <t>21,700</t>
         </is>
       </c>
+      <c r="AP29" s="2" t="inlineStr">
+        <is>
+          <t>21,800</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6679,6 +6825,11 @@
           <t>18,000</t>
         </is>
       </c>
+      <c r="AP30" s="2" t="inlineStr">
+        <is>
+          <t>18,050</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6886,6 +7037,11 @@
           <t>18,700</t>
         </is>
       </c>
+      <c r="AP31" s="2" t="inlineStr">
+        <is>
+          <t>18,700</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -7091,6 +7247,11 @@
       <c r="AO32" s="2" t="inlineStr">
         <is>
           <t>17,550</t>
+        </is>
+      </c>
+      <c r="AP32" s="2" t="inlineStr">
+        <is>
+          <t>17,600</t>
         </is>
       </c>
     </row>

--- a/Dataset/Food Prices/PIHPS/Wholesale/Tabel Harga Berdasarkan Daerah 2026.xlsx
+++ b/Dataset/Food Prices/PIHPS/Wholesale/Tabel Harga Berdasarkan Daerah 2026.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP32"/>
+  <dimension ref="A1:AQ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.43" customWidth="1" min="1" max="1"/>
@@ -469,6 +469,7 @@
     <col width="8.859999999999999" customWidth="1" min="40" max="40"/>
     <col width="8.859999999999999" customWidth="1" min="41" max="41"/>
     <col width="8.859999999999999" customWidth="1" min="42" max="42"/>
+    <col width="8.859999999999999" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -682,6 +683,11 @@
           <t>01/ 10/ 2026</t>
         </is>
       </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>08/ 10/ 2026</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -894,6 +900,11 @@
           <t>15,500</t>
         </is>
       </c>
+      <c r="AQ2" s="2" t="inlineStr">
+        <is>
+          <t>15,500</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1106,6 +1117,11 @@
           <t>14,450</t>
         </is>
       </c>
+      <c r="AQ3" s="2" t="inlineStr">
+        <is>
+          <t>14,450</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1318,6 +1334,11 @@
           <t>14,000</t>
         </is>
       </c>
+      <c r="AQ4" s="2" t="inlineStr">
+        <is>
+          <t>14,000</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1530,6 +1551,11 @@
           <t>15,600</t>
         </is>
       </c>
+      <c r="AQ5" s="2" t="inlineStr">
+        <is>
+          <t>15,600</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1742,6 +1768,11 @@
           <t>15,450</t>
         </is>
       </c>
+      <c r="AQ6" s="2" t="inlineStr">
+        <is>
+          <t>15,450</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1954,6 +1985,11 @@
           <t>16,850</t>
         </is>
       </c>
+      <c r="AQ7" s="2" t="inlineStr">
+        <is>
+          <t>16,850</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2166,6 +2202,11 @@
           <t>16,400</t>
         </is>
       </c>
+      <c r="AQ8" s="2" t="inlineStr">
+        <is>
+          <t>16,400</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2378,6 +2419,11 @@
           <t>35,550</t>
         </is>
       </c>
+      <c r="AQ9" s="2" t="inlineStr">
+        <is>
+          <t>34,950</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2590,6 +2636,11 @@
           <t>35,550</t>
         </is>
       </c>
+      <c r="AQ10" s="2" t="inlineStr">
+        <is>
+          <t>34,950</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2802,6 +2853,11 @@
           <t>139,800</t>
         </is>
       </c>
+      <c r="AQ11" s="2" t="inlineStr">
+        <is>
+          <t>139,850</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3014,6 +3070,11 @@
           <t>143,850</t>
         </is>
       </c>
+      <c r="AQ12" s="2" t="inlineStr">
+        <is>
+          <t>143,900</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3226,6 +3287,11 @@
           <t>135,000</t>
         </is>
       </c>
+      <c r="AQ13" s="2" t="inlineStr">
+        <is>
+          <t>135,050</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3438,6 +3504,11 @@
           <t>26,200</t>
         </is>
       </c>
+      <c r="AQ14" s="2" t="inlineStr">
+        <is>
+          <t>25,950</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3650,6 +3721,11 @@
           <t>26,200</t>
         </is>
       </c>
+      <c r="AQ15" s="2" t="inlineStr">
+        <is>
+          <t>25,950</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3862,6 +3938,11 @@
           <t>29,150</t>
         </is>
       </c>
+      <c r="AQ16" s="2" t="inlineStr">
+        <is>
+          <t>28,900</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -4074,6 +4155,11 @@
           <t>29,150</t>
         </is>
       </c>
+      <c r="AQ17" s="2" t="inlineStr">
+        <is>
+          <t>28,900</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4286,6 +4372,11 @@
           <t>30,550</t>
         </is>
       </c>
+      <c r="AQ18" s="2" t="inlineStr">
+        <is>
+          <t>30,300</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4498,6 +4589,11 @@
           <t>30,550</t>
         </is>
       </c>
+      <c r="AQ19" s="2" t="inlineStr">
+        <is>
+          <t>30,300</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4710,6 +4806,11 @@
           <t>59,500</t>
         </is>
       </c>
+      <c r="AQ20" s="2" t="inlineStr">
+        <is>
+          <t>69,200</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4922,6 +5023,11 @@
           <t>49,850</t>
         </is>
       </c>
+      <c r="AQ21" s="2" t="inlineStr">
+        <is>
+          <t>57,450</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -5134,6 +5240,11 @@
           <t>62,550</t>
         </is>
       </c>
+      <c r="AQ22" s="2" t="inlineStr">
+        <is>
+          <t>72,650</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5346,6 +5457,11 @@
           <t>74,900</t>
         </is>
       </c>
+      <c r="AQ23" s="2" t="inlineStr">
+        <is>
+          <t>78,400</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5558,6 +5674,11 @@
           <t>61,250</t>
         </is>
       </c>
+      <c r="AQ24" s="2" t="inlineStr">
+        <is>
+          <t>66,400</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5770,6 +5891,11 @@
           <t>84,850</t>
         </is>
       </c>
+      <c r="AQ25" s="2" t="inlineStr">
+        <is>
+          <t>87,300</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5982,6 +6108,11 @@
           <t>21,100</t>
         </is>
       </c>
+      <c r="AQ26" s="2" t="inlineStr">
+        <is>
+          <t>21,050</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -6194,6 +6325,11 @@
           <t>18,700</t>
         </is>
       </c>
+      <c r="AQ27" s="2" t="inlineStr">
+        <is>
+          <t>18,650</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -6406,6 +6542,11 @@
           <t>22,150</t>
         </is>
       </c>
+      <c r="AQ28" s="2" t="inlineStr">
+        <is>
+          <t>22,150</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6618,6 +6759,11 @@
           <t>21,800</t>
         </is>
       </c>
+      <c r="AQ29" s="2" t="inlineStr">
+        <is>
+          <t>21,800</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6830,6 +6976,11 @@
           <t>18,050</t>
         </is>
       </c>
+      <c r="AQ30" s="2" t="inlineStr">
+        <is>
+          <t>18,100</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -7042,6 +7193,11 @@
           <t>18,700</t>
         </is>
       </c>
+      <c r="AQ31" s="2" t="inlineStr">
+        <is>
+          <t>18,700</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -7252,6 +7408,11 @@
       <c r="AP32" s="2" t="inlineStr">
         <is>
           <t>17,600</t>
+        </is>
+      </c>
+      <c r="AQ32" s="2" t="inlineStr">
+        <is>
+          <t>17,700</t>
         </is>
       </c>
     </row>

--- a/Dataset/Food Prices/PIHPS/Wholesale/Tabel Harga Berdasarkan Daerah 2026.xlsx
+++ b/Dataset/Food Prices/PIHPS/Wholesale/Tabel Harga Berdasarkan Daerah 2026.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ32"/>
+  <dimension ref="A1:AR32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.43" customWidth="1" min="1" max="1"/>
@@ -470,6 +470,7 @@
     <col width="8.859999999999999" customWidth="1" min="41" max="41"/>
     <col width="8.859999999999999" customWidth="1" min="42" max="42"/>
     <col width="8.859999999999999" customWidth="1" min="43" max="43"/>
+    <col width="8.859999999999999" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -688,6 +689,11 @@
           <t>08/ 10/ 2026</t>
         </is>
       </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>15/ 10/ 2026</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -905,6 +911,11 @@
           <t>15,500</t>
         </is>
       </c>
+      <c r="AR2" s="2" t="inlineStr">
+        <is>
+          <t>15,500</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1122,6 +1133,11 @@
           <t>14,450</t>
         </is>
       </c>
+      <c r="AR3" s="2" t="inlineStr">
+        <is>
+          <t>14,450</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1339,6 +1355,11 @@
           <t>14,000</t>
         </is>
       </c>
+      <c r="AR4" s="2" t="inlineStr">
+        <is>
+          <t>14,000</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1556,6 +1577,11 @@
           <t>15,600</t>
         </is>
       </c>
+      <c r="AR5" s="2" t="inlineStr">
+        <is>
+          <t>15,600</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1773,6 +1799,11 @@
           <t>15,450</t>
         </is>
       </c>
+      <c r="AR6" s="2" t="inlineStr">
+        <is>
+          <t>15,500</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1990,6 +2021,11 @@
           <t>16,850</t>
         </is>
       </c>
+      <c r="AR7" s="2" t="inlineStr">
+        <is>
+          <t>16,850</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2207,6 +2243,11 @@
           <t>16,400</t>
         </is>
       </c>
+      <c r="AR8" s="2" t="inlineStr">
+        <is>
+          <t>16,400</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2424,6 +2465,11 @@
           <t>34,950</t>
         </is>
       </c>
+      <c r="AR9" s="2" t="inlineStr">
+        <is>
+          <t>34,550</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2641,6 +2687,11 @@
           <t>34,950</t>
         </is>
       </c>
+      <c r="AR10" s="2" t="inlineStr">
+        <is>
+          <t>34,550</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2858,6 +2909,11 @@
           <t>139,850</t>
         </is>
       </c>
+      <c r="AR11" s="2" t="inlineStr">
+        <is>
+          <t>139,950</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3075,6 +3131,11 @@
           <t>143,900</t>
         </is>
       </c>
+      <c r="AR12" s="2" t="inlineStr">
+        <is>
+          <t>143,900</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3292,6 +3353,11 @@
           <t>135,050</t>
         </is>
       </c>
+      <c r="AR13" s="2" t="inlineStr">
+        <is>
+          <t>135,250</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3509,6 +3575,11 @@
           <t>25,950</t>
         </is>
       </c>
+      <c r="AR14" s="2" t="inlineStr">
+        <is>
+          <t>26,000</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3726,6 +3797,11 @@
           <t>25,950</t>
         </is>
       </c>
+      <c r="AR15" s="2" t="inlineStr">
+        <is>
+          <t>26,000</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3943,6 +4019,11 @@
           <t>28,900</t>
         </is>
       </c>
+      <c r="AR16" s="2" t="inlineStr">
+        <is>
+          <t>29,050</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -4160,6 +4241,11 @@
           <t>28,900</t>
         </is>
       </c>
+      <c r="AR17" s="2" t="inlineStr">
+        <is>
+          <t>29,050</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4377,6 +4463,11 @@
           <t>30,300</t>
         </is>
       </c>
+      <c r="AR18" s="2" t="inlineStr">
+        <is>
+          <t>30,250</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4594,6 +4685,11 @@
           <t>30,300</t>
         </is>
       </c>
+      <c r="AR19" s="2" t="inlineStr">
+        <is>
+          <t>30,250</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4811,6 +4907,11 @@
           <t>69,200</t>
         </is>
       </c>
+      <c r="AR20" s="2" t="inlineStr">
+        <is>
+          <t>71,550</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -5028,6 +5129,11 @@
           <t>57,450</t>
         </is>
       </c>
+      <c r="AR21" s="2" t="inlineStr">
+        <is>
+          <t>61,700</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -5245,6 +5351,11 @@
           <t>72,650</t>
         </is>
       </c>
+      <c r="AR22" s="2" t="inlineStr">
+        <is>
+          <t>74,150</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5462,6 +5573,11 @@
           <t>78,400</t>
         </is>
       </c>
+      <c r="AR23" s="2" t="inlineStr">
+        <is>
+          <t>80,100</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5679,6 +5795,11 @@
           <t>66,400</t>
         </is>
       </c>
+      <c r="AR24" s="2" t="inlineStr">
+        <is>
+          <t>69,600</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5896,6 +6017,11 @@
           <t>87,300</t>
         </is>
       </c>
+      <c r="AR25" s="2" t="inlineStr">
+        <is>
+          <t>87,300</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -6113,6 +6239,11 @@
           <t>21,050</t>
         </is>
       </c>
+      <c r="AR26" s="2" t="inlineStr">
+        <is>
+          <t>21,050</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -6330,6 +6461,11 @@
           <t>18,650</t>
         </is>
       </c>
+      <c r="AR27" s="2" t="inlineStr">
+        <is>
+          <t>18,600</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -6547,6 +6683,11 @@
           <t>22,150</t>
         </is>
       </c>
+      <c r="AR28" s="2" t="inlineStr">
+        <is>
+          <t>22,150</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6764,6 +6905,11 @@
           <t>21,800</t>
         </is>
       </c>
+      <c r="AR29" s="2" t="inlineStr">
+        <is>
+          <t>21,800</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6981,6 +7127,11 @@
           <t>18,100</t>
         </is>
       </c>
+      <c r="AR30" s="2" t="inlineStr">
+        <is>
+          <t>18,150</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -7198,6 +7349,11 @@
           <t>18,700</t>
         </is>
       </c>
+      <c r="AR31" s="2" t="inlineStr">
+        <is>
+          <t>18,700</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -7411,6 +7567,11 @@
         </is>
       </c>
       <c r="AQ32" s="2" t="inlineStr">
+        <is>
+          <t>17,700</t>
+        </is>
+      </c>
+      <c r="AR32" s="2" t="inlineStr">
         <is>
           <t>17,700</t>
         </is>

--- a/Dataset/Food Prices/PIHPS/Wholesale/Tabel Harga Berdasarkan Daerah 2026.xlsx
+++ b/Dataset/Food Prices/PIHPS/Wholesale/Tabel Harga Berdasarkan Daerah 2026.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR32"/>
+  <dimension ref="A1:AS32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.43" customWidth="1" min="1" max="1"/>
@@ -471,6 +471,7 @@
     <col width="8.859999999999999" customWidth="1" min="42" max="42"/>
     <col width="8.859999999999999" customWidth="1" min="43" max="43"/>
     <col width="8.859999999999999" customWidth="1" min="44" max="44"/>
+    <col width="8.859999999999999" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,6 +695,11 @@
           <t>15/ 10/ 2026</t>
         </is>
       </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>22/ 10/ 2026</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -916,6 +922,11 @@
           <t>15,500</t>
         </is>
       </c>
+      <c r="AS2" s="2" t="inlineStr">
+        <is>
+          <t>15,500</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1138,6 +1149,11 @@
           <t>14,450</t>
         </is>
       </c>
+      <c r="AS3" s="2" t="inlineStr">
+        <is>
+          <t>14,450</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1360,6 +1376,11 @@
           <t>14,000</t>
         </is>
       </c>
+      <c r="AS4" s="2" t="inlineStr">
+        <is>
+          <t>14,000</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1582,6 +1603,11 @@
           <t>15,600</t>
         </is>
       </c>
+      <c r="AS5" s="2" t="inlineStr">
+        <is>
+          <t>15,600</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1804,6 +1830,11 @@
           <t>15,500</t>
         </is>
       </c>
+      <c r="AS6" s="2" t="inlineStr">
+        <is>
+          <t>15,450</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2026,6 +2057,11 @@
           <t>16,850</t>
         </is>
       </c>
+      <c r="AS7" s="2" t="inlineStr">
+        <is>
+          <t>16,850</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2248,6 +2284,11 @@
           <t>16,400</t>
         </is>
       </c>
+      <c r="AS8" s="2" t="inlineStr">
+        <is>
+          <t>16,400</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2470,6 +2511,11 @@
           <t>34,550</t>
         </is>
       </c>
+      <c r="AS9" s="2" t="inlineStr">
+        <is>
+          <t>33,950</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2692,6 +2738,11 @@
           <t>34,550</t>
         </is>
       </c>
+      <c r="AS10" s="2" t="inlineStr">
+        <is>
+          <t>33,950</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2914,6 +2965,11 @@
           <t>139,950</t>
         </is>
       </c>
+      <c r="AS11" s="2" t="inlineStr">
+        <is>
+          <t>139,600</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3136,6 +3192,11 @@
           <t>143,900</t>
         </is>
       </c>
+      <c r="AS12" s="2" t="inlineStr">
+        <is>
+          <t>143,650</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3358,6 +3419,11 @@
           <t>135,250</t>
         </is>
       </c>
+      <c r="AS13" s="2" t="inlineStr">
+        <is>
+          <t>134,800</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3580,6 +3646,11 @@
           <t>26,000</t>
         </is>
       </c>
+      <c r="AS14" s="2" t="inlineStr">
+        <is>
+          <t>25,750</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3802,6 +3873,11 @@
           <t>26,000</t>
         </is>
       </c>
+      <c r="AS15" s="2" t="inlineStr">
+        <is>
+          <t>25,750</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -4024,6 +4100,11 @@
           <t>29,050</t>
         </is>
       </c>
+      <c r="AS16" s="2" t="inlineStr">
+        <is>
+          <t>29,200</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -4246,6 +4327,11 @@
           <t>29,050</t>
         </is>
       </c>
+      <c r="AS17" s="2" t="inlineStr">
+        <is>
+          <t>29,200</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4468,6 +4554,11 @@
           <t>30,250</t>
         </is>
       </c>
+      <c r="AS18" s="2" t="inlineStr">
+        <is>
+          <t>30,150</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4690,6 +4781,11 @@
           <t>30,250</t>
         </is>
       </c>
+      <c r="AS19" s="2" t="inlineStr">
+        <is>
+          <t>30,150</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4912,6 +5008,11 @@
           <t>71,550</t>
         </is>
       </c>
+      <c r="AS20" s="2" t="inlineStr">
+        <is>
+          <t>70,150</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -5134,6 +5235,11 @@
           <t>61,700</t>
         </is>
       </c>
+      <c r="AS21" s="2" t="inlineStr">
+        <is>
+          <t>60,000</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -5356,6 +5462,11 @@
           <t>74,150</t>
         </is>
       </c>
+      <c r="AS22" s="2" t="inlineStr">
+        <is>
+          <t>73,050</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5578,6 +5689,11 @@
           <t>80,100</t>
         </is>
       </c>
+      <c r="AS23" s="2" t="inlineStr">
+        <is>
+          <t>80,200</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5800,6 +5916,11 @@
           <t>69,600</t>
         </is>
       </c>
+      <c r="AS24" s="2" t="inlineStr">
+        <is>
+          <t>70,000</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -6022,6 +6143,11 @@
           <t>87,300</t>
         </is>
       </c>
+      <c r="AS25" s="2" t="inlineStr">
+        <is>
+          <t>87,000</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -6244,6 +6370,11 @@
           <t>21,050</t>
         </is>
       </c>
+      <c r="AS26" s="2" t="inlineStr">
+        <is>
+          <t>21,050</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -6466,6 +6597,11 @@
           <t>18,600</t>
         </is>
       </c>
+      <c r="AS27" s="2" t="inlineStr">
+        <is>
+          <t>18,550</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -6688,6 +6824,11 @@
           <t>22,150</t>
         </is>
       </c>
+      <c r="AS28" s="2" t="inlineStr">
+        <is>
+          <t>22,100</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6910,6 +7051,11 @@
           <t>21,800</t>
         </is>
       </c>
+      <c r="AS29" s="2" t="inlineStr">
+        <is>
+          <t>21,750</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -7132,6 +7278,11 @@
           <t>18,150</t>
         </is>
       </c>
+      <c r="AS30" s="2" t="inlineStr">
+        <is>
+          <t>18,250</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -7354,6 +7505,11 @@
           <t>18,700</t>
         </is>
       </c>
+      <c r="AS31" s="2" t="inlineStr">
+        <is>
+          <t>18,750</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -7574,6 +7730,11 @@
       <c r="AR32" s="2" t="inlineStr">
         <is>
           <t>17,700</t>
+        </is>
+      </c>
+      <c r="AS32" s="2" t="inlineStr">
+        <is>
+          <t>17,850</t>
         </is>
       </c>
     </row>

--- a/Dataset/Food Prices/PIHPS/Wholesale/Tabel Harga Berdasarkan Daerah 2026.xlsx
+++ b/Dataset/Food Prices/PIHPS/Wholesale/Tabel Harga Berdasarkan Daerah 2026.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS32"/>
+  <dimension ref="A1:AT32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.43" customWidth="1" min="1" max="1"/>
@@ -472,6 +472,7 @@
     <col width="8.859999999999999" customWidth="1" min="43" max="43"/>
     <col width="8.859999999999999" customWidth="1" min="44" max="44"/>
     <col width="8.859999999999999" customWidth="1" min="45" max="45"/>
+    <col width="8.859999999999999" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -700,6 +701,11 @@
           <t>22/ 10/ 2026</t>
         </is>
       </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>29/ 10/ 2026</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -927,6 +933,11 @@
           <t>15,500</t>
         </is>
       </c>
+      <c r="AT2" s="2" t="inlineStr">
+        <is>
+          <t>15,500</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1154,6 +1165,11 @@
           <t>14,450</t>
         </is>
       </c>
+      <c r="AT3" s="2" t="inlineStr">
+        <is>
+          <t>14,450</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1381,6 +1397,11 @@
           <t>14,000</t>
         </is>
       </c>
+      <c r="AT4" s="2" t="inlineStr">
+        <is>
+          <t>14,000</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1608,6 +1629,11 @@
           <t>15,600</t>
         </is>
       </c>
+      <c r="AT5" s="2" t="inlineStr">
+        <is>
+          <t>15,650</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1835,6 +1861,11 @@
           <t>15,450</t>
         </is>
       </c>
+      <c r="AT6" s="2" t="inlineStr">
+        <is>
+          <t>15,450</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2062,6 +2093,11 @@
           <t>16,850</t>
         </is>
       </c>
+      <c r="AT7" s="2" t="inlineStr">
+        <is>
+          <t>16,850</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2289,6 +2325,11 @@
           <t>16,400</t>
         </is>
       </c>
+      <c r="AT8" s="2" t="inlineStr">
+        <is>
+          <t>16,400</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2516,6 +2557,11 @@
           <t>33,950</t>
         </is>
       </c>
+      <c r="AT9" s="2" t="inlineStr">
+        <is>
+          <t>32,950</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2743,6 +2789,11 @@
           <t>33,950</t>
         </is>
       </c>
+      <c r="AT10" s="2" t="inlineStr">
+        <is>
+          <t>32,950</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2970,6 +3021,11 @@
           <t>139,600</t>
         </is>
       </c>
+      <c r="AT11" s="2" t="inlineStr">
+        <is>
+          <t>139,850</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3197,6 +3253,11 @@
           <t>143,650</t>
         </is>
       </c>
+      <c r="AT12" s="2" t="inlineStr">
+        <is>
+          <t>143,900</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3424,6 +3485,11 @@
           <t>134,800</t>
         </is>
       </c>
+      <c r="AT13" s="2" t="inlineStr">
+        <is>
+          <t>135,000</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3651,6 +3717,11 @@
           <t>25,750</t>
         </is>
       </c>
+      <c r="AT14" s="2" t="inlineStr">
+        <is>
+          <t>25,650</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3878,6 +3949,11 @@
           <t>25,750</t>
         </is>
       </c>
+      <c r="AT15" s="2" t="inlineStr">
+        <is>
+          <t>25,650</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -4105,6 +4181,11 @@
           <t>29,200</t>
         </is>
       </c>
+      <c r="AT16" s="2" t="inlineStr">
+        <is>
+          <t>29,100</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -4332,6 +4413,11 @@
           <t>29,200</t>
         </is>
       </c>
+      <c r="AT17" s="2" t="inlineStr">
+        <is>
+          <t>29,100</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4559,6 +4645,11 @@
           <t>30,150</t>
         </is>
       </c>
+      <c r="AT18" s="2" t="inlineStr">
+        <is>
+          <t>29,850</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4786,6 +4877,11 @@
           <t>30,150</t>
         </is>
       </c>
+      <c r="AT19" s="2" t="inlineStr">
+        <is>
+          <t>29,850</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -5013,6 +5109,11 @@
           <t>70,150</t>
         </is>
       </c>
+      <c r="AT20" s="2" t="inlineStr">
+        <is>
+          <t>69,150</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -5240,6 +5341,11 @@
           <t>60,000</t>
         </is>
       </c>
+      <c r="AT21" s="2" t="inlineStr">
+        <is>
+          <t>58,050</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -5467,6 +5573,11 @@
           <t>73,050</t>
         </is>
       </c>
+      <c r="AT22" s="2" t="inlineStr">
+        <is>
+          <t>72,150</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5694,6 +5805,11 @@
           <t>80,200</t>
         </is>
       </c>
+      <c r="AT23" s="2" t="inlineStr">
+        <is>
+          <t>77,400</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5921,6 +6037,11 @@
           <t>70,000</t>
         </is>
       </c>
+      <c r="AT24" s="2" t="inlineStr">
+        <is>
+          <t>69,300</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -6148,6 +6269,11 @@
           <t>87,000</t>
         </is>
       </c>
+      <c r="AT25" s="2" t="inlineStr">
+        <is>
+          <t>82,650</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -6375,6 +6501,11 @@
           <t>21,050</t>
         </is>
       </c>
+      <c r="AT26" s="2" t="inlineStr">
+        <is>
+          <t>21,050</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -6602,6 +6733,11 @@
           <t>18,550</t>
         </is>
       </c>
+      <c r="AT27" s="2" t="inlineStr">
+        <is>
+          <t>18,550</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -6829,6 +6965,11 @@
           <t>22,100</t>
         </is>
       </c>
+      <c r="AT28" s="2" t="inlineStr">
+        <is>
+          <t>22,050</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -7056,6 +7197,11 @@
           <t>21,750</t>
         </is>
       </c>
+      <c r="AT29" s="2" t="inlineStr">
+        <is>
+          <t>21,750</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -7283,6 +7429,11 @@
           <t>18,250</t>
         </is>
       </c>
+      <c r="AT30" s="2" t="inlineStr">
+        <is>
+          <t>18,300</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -7510,6 +7661,11 @@
           <t>18,750</t>
         </is>
       </c>
+      <c r="AT31" s="2" t="inlineStr">
+        <is>
+          <t>18,750</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -7735,6 +7891,11 @@
       <c r="AS32" s="2" t="inlineStr">
         <is>
           <t>17,850</t>
+        </is>
+      </c>
+      <c r="AT32" s="2" t="inlineStr">
+        <is>
+          <t>17,950</t>
         </is>
       </c>
     </row>
